--- a/stories/arbres/ATOM-COL.POL.001-13.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-13.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Georges va à la boulangerie. Papa tient sa main. Ça sent le pain chaud. Georges dit : bonjour. La dame sourit. Georges dit : un pain, s'il te plaît. La dame tend le pain. Georges dit : merci. Papa dit : bonjour. S'il te plaît. Merci. Georges répète. Le pain est chaud. Papa dit merci aussi.</t>
+          <t>Georges va à la boulangerie. Papa tient sa main. Ça sent le pain chaud. Bonjour. La dame sourit. Un pain, s'il te plaît. La dame tend le pain. Merci. Bonjour. S'il te plaît. Merci. Georges répète. Le pain est chaud. Papa dit merci aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Georges va à la boulangerie. Papa tient sa main. Ça sent le pain chaud.
+enfant-m|Bonjour.
+narrateur|La dame sourit.
+enfant-m|Un pain, s'il te plaît.
+narrateur|La dame tend le pain.
+enfant-m|Merci.
+papa|Bonjour. S'il te plaît. Merci.
+narrateur|Georges répète. Le pain est chaud. Papa dit merci aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Georges parle à la dame. Quels mots dit-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Georges a dit bonjour. Il a dit s'il te plaît. Il a dit merci. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1829,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Georges tient le pain. Papa ouvre la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.POL.001-13.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-13.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Georges répète. Le pain est chaud. Papa dit merci aussi.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Georges parle à la dame. Quels mots dit-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Georges a dit bonjour. Il a dit s'il te plaît. Il a dit merci. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Georges tient le pain. Papa ouvre la porte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-COL.POL.001-13.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-13.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Georges dit bonjour s'il te plaît merci</t>
+          <t>Le pain chaud de Victorino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino voit les pains dorés derrière la vitre floue. Il tient la main de papa. Il dit bonjour, s'il te plaît, merci. Le sachet reste chaud.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Georges va à la boulangerie. Papa tient sa main. Ça sent le pain chaud. Bonjour. La dame sourit. Un pain, s'il te plaît. La dame tend le pain. Merci. Bonjour. S'il te plaît. Merci. Georges répète. Le pain est chaud. Papa dit merci aussi.</t>
+          <t>La vitre de la boulangerie est floue. Derrière, les pains sont dorés. Une odeur de beurre passe dehors. Le trottoir est encore mouillé. Une petite flaque brille. Tu as vu la flaque, Victorino ? Oui, papa. En ce moment, Victorino tient la main de papa. Ils avancent vers la porte. La cloche fait ding. On est arrivés. L'air est chaud, dedans. Ça sent bon. Oui. Le pain est chaud. La dame est derrière le comptoir. On dit bonjour ? Bonjour. Bonjour. La dame écoute. Tu veux un pain ? Oui. On dit s'il te plaît. Un pain, s'il te plaît. La dame prend un pain doré. Elle le met dans un sachet. Le sachet craque un peu. Merci. Merci. Bravo, Victorino. Tu as dit les mots. Victorino tient le sachet. Le pain est encore chaud. Il est chaud, papa. Oui. On le sent. Tu as dit bonjour. Tu as dit s'il te plaît. Tu as dit merci. Bonjour. S'il te plaît. Merci. C'est ça. Bravo. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1324,53 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Georges va à la boulangerie. Papa tient sa main. Ça sent le pain chaud.
+          <t>narrateur|La vitre de la boulangerie est floue.
+narrateur|Derrière, les pains sont dorés.
+narrateur|Une odeur de beurre passe dehors.
+narrateur|Le trottoir est encore mouillé.
+narrateur|Une petite flaque brille.
+papa|Tu as vu la flaque, Victorino ?
+enfant-m|Oui, papa.
+narrateur|En ce moment, Victorino tient la main de papa.
+narrateur|Ils avancent vers la porte.
+narrateur|La cloche fait ding.
+papa|On est arrivés.
+narrateur|L'air est chaud, dedans.
+enfant-m|Ça sent bon.
+papa|Oui. Le pain est chaud.
+narrateur|La dame est derrière le comptoir.
+papa|On dit bonjour ?
 enfant-m|Bonjour.
-narrateur|La dame sourit.
+papa|Bonjour.
+narrateur|La dame écoute.
+papa|Tu veux un pain ?
+enfant-m|Oui.
+papa|On dit s'il te plaît.
 enfant-m|Un pain, s'il te plaît.
-narrateur|La dame tend le pain.
+narrateur|La dame prend un pain doré.
+narrateur|Elle le met dans un sachet.
+narrateur|Le sachet craque un peu.
 enfant-m|Merci.
-papa|Bonjour. S'il te plaît. Merci.
-narrateur|Georges répète. Le pain est chaud. Papa dit merci aussi.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Merci.
+papa|Bravo, Victorino.
+papa|Tu as dit les mots.
+narrateur|Victorino tient le sachet.
+narrateur|Le pain est encore chaud.
+enfant-m|Il est chaud, papa.
+papa|Oui. On le sent.
+papa|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+papa|Tu as dit merci.
+enfant-m|Bonjour. S'il te plaît. Merci.
+papa|C'est ça. Bravo.
+papa|Tu as fait du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cloche,pain,porte</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,7 +1395,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Georges parle à la dame. Quels mots dit-il ?</t>
+          <t>Victorino parle à la dame. Quels mots dit-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,7 +1551,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Georges parle à la dame. Quels mots dit-il ?</t>
+          <t>narrateur|Victorino parle à la dame.
+narrateur|Quels mots dit-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1580,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Georges a dit bonjour. Il a dit s'il te plaît. Il a dit merci. Papa était là.</t>
+          <t>Victorino a dit bonjour. Il a dit s'il te plaît. Il a dit merci. Tu as dit les trois mots. Bravo. Bonjour. S'il te plaît. Merci. Oui. C'est ça. Le sachet reste chaud. Victorino le serre. Tu as fini de tenir le pain ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,7 +1724,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Georges a dit bonjour. Il a dit s'il te plaît. Il a dit merci. Papa était là.</t>
+          <t>narrateur|Victorino a dit bonjour.
+narrateur|Il a dit s'il te plaît.
+narrateur|Il a dit merci.
+papa|Tu as dit les trois mots.
+papa|Bravo.
+enfant-m|Bonjour. S'il te plaît. Merci.
+papa|Oui. C'est ça.
+narrateur|Le sachet reste chaud.
+narrateur|Victorino le serre.
+papa|Tu as fini de tenir le pain ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1762,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Georges tient le pain. Papa ouvre la porte.</t>
+          <t>Papa ouvre la porte. La cloche fait ding, encore. L'air dehors est plus frais. Le pain est à moi. On le porte ensemble. Victorino tient le sachet. Papa tient sa main. Merci, Victorino. Merci, papa. On rentre ? Oui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,10 +1898,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Georges tient le pain. Papa ouvre la porte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa ouvre la porte.
+narrateur|La cloche fait ding, encore.
+narrateur|L'air dehors est plus frais.
+enfant-m|Le pain est à moi.
+papa|On le porte ensemble.
+narrateur|Victorino tient le sachet.
+narrateur|Papa tient sa main.
+papa|Merci, Victorino.
+enfant-m|Merci, papa.
+papa|On rentre ?
+enfant-m|Oui.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>porte,cloche</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,7 +1940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit bonjour. S'il te plaît. Merci. Bravo. Tu as fait du bon travail. Le pain est à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,7 +2080,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit bonjour.
+enfant-m|S'il te plaît. Merci.
+papa|Bravo. Tu as fait du bon travail.
+narrateur|Le pain est à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2144,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.POL.001-13.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-13.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la boulangerie est floue. Derrière, les pains sont dorés. Une odeur de beurre passe dehors. Le trottoir est encore mouillé. Une petite flaque brille. Tu as vu la flaque, Victorino ? Oui, papa. En ce moment, Victorino tient la main de papa. Ils avancent vers la porte. La cloche fait ding. On est arrivés. L'air est chaud, dedans. Ça sent bon. Oui. Le pain est chaud. La dame est derrière le comptoir. On dit bonjour ? Bonjour. Bonjour. La dame écoute. Tu veux un pain ? Oui. On dit s'il te plaît. Un pain, s'il te plaît. La dame prend un pain doré. Elle le met dans un sachet. Le sachet craque un peu. Merci. Merci. Bravo, Victorino. Tu as dit les mots. Victorino tient le sachet. Le pain est encore chaud. Il est chaud, papa. Oui. On le sent. Tu as dit bonjour. Tu as dit s'il te plaît. Tu as dit merci. Bonjour. S'il te plaît. Merci. C'est ça. Bravo. Tu as fait du bon travail.</t>
+          <t>La vitre de la boulangerie est floue. Derrière, les pains sont dorés. Une odeur de beurre passe dehors. Le trottoir est encore mouillé. Une petite flaque brille. Tu as vu la flaque, Victorino ? Oui, papa. En ce moment, Victorino tient la main de papa. Ils avancent vers la porte. La cloche fait ding. On est arrivés. L'air est chaud, dedans. De la farine blanche dort sur le bois. Une baguette se tient debout. Victorino monte un peu sur la pointe. Ça sent bon. Oui. Le pain est chaud. Tu as vu la baguette ? Elle est grande. La dame est derrière le comptoir. On dit bonjour ? Bonjour. Bonjour. La dame écoute. Tu veux un pain ? Oui. On dit s'il te plaît. Un pain, s'il te plaît. La dame prend un pain doré. Elle le met dans un sachet. Le sachet craque un peu. Merci. Merci. Bravo, Victorino. Tu as dit les mots. Victorino tient le sachet. Le pain est encore chaud. Il est chaud, papa. Oui. On le sent. Tu as dit bonjour. Tu as dit s'il te plaît. Tu as dit merci. Bonjour. S'il te plaît. Merci. C'est ça. Bravo. Tu as fait du bon travail. Victorino pose le sachet contre sa veste. La chaleur passe un peu. On reste encore un petit moment ? Oui. Je tiens le pain.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1336,8 +1336,14 @@
 narrateur|La cloche fait ding.
 papa|On est arrivés.
 narrateur|L'air est chaud, dedans.
+narrateur|De la farine blanche dort sur le bois.
+narrateur|Une baguette se tient debout.
+narrateur|Victorino monte un peu sur la pointe.
 enfant-m|Ça sent bon.
-papa|Oui. Le pain est chaud.
+papa|Oui.
+papa|Le pain est chaud.
+papa|Tu as vu la baguette ?
+enfant-m|Elle est grande.
 narrateur|La dame est derrière le comptoir.
 papa|On dit bonjour ?
 enfant-m|Bonjour.
@@ -1357,13 +1363,22 @@
 narrateur|Victorino tient le sachet.
 narrateur|Le pain est encore chaud.
 enfant-m|Il est chaud, papa.
-papa|Oui. On le sent.
+papa|Oui.
+papa|On le sent.
 papa|Tu as dit bonjour.
 papa|Tu as dit s'il te plaît.
 papa|Tu as dit merci.
-enfant-m|Bonjour. S'il te plaît. Merci.
-papa|C'est ça. Bravo.
-papa|Tu as fait du bon travail.</t>
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+papa|C'est ça.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Victorino pose le sachet contre sa veste.
+narrateur|La chaleur passe un peu.
+papa|On reste encore un petit moment ?
+enfant-m|Oui.
+enfant-m|Je tiens le pain.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1729,8 +1744,11 @@
 narrateur|Il a dit merci.
 papa|Tu as dit les trois mots.
 papa|Bravo.
-enfant-m|Bonjour. S'il te plaît. Merci.
-papa|Oui. C'est ça.
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+papa|Oui.
+papa|C'est ça.
 narrateur|Le sachet reste chaud.
 narrateur|Victorino le serre.
 papa|Tu as fini de tenir le pain ?
@@ -2081,8 +2099,10 @@
       <c r="AW6" t="inlineStr">
         <is>
           <t>enfant-m|J'ai dit bonjour.
-enfant-m|S'il te plaît. Merci.
-papa|Bravo. Tu as fait du bon travail.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 narrateur|Le pain est à la maison.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -2106,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2149,6 +2169,34 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-COL.POL.001-13.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-13.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le pain chaud de Victorino</t>
+          <t>Le cacao de Victorino</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>COL.ECO.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -841,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Victorino voit les pains dorés derrière la vitre floue. Il tient la main de papa. Il dit bonjour, s'il te plaît, merci. Le sachet reste chaud.</t>
+          <t>Victorino veut la tasse de cacao derrière la vitre. Il dit bonjour, s'il te plaît, merci. La mousse laisse un point sur son nez.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la boulangerie est floue. Derrière, les pains sont dorés. Une odeur de beurre passe dehors. Le trottoir est encore mouillé. Une petite flaque brille. Tu as vu la flaque, Victorino ? Oui, papa. En ce moment, Victorino tient la main de papa. Ils avancent vers la porte. La cloche fait ding. On est arrivés. L'air est chaud, dedans. De la farine blanche dort sur le bois. Une baguette se tient debout. Victorino monte un peu sur la pointe. Ça sent bon. Oui. Le pain est chaud. Tu as vu la baguette ? Elle est grande. La dame est derrière le comptoir. On dit bonjour ? Bonjour. Bonjour. La dame écoute. Tu veux un pain ? Oui. On dit s'il te plaît. Un pain, s'il te plaît. La dame prend un pain doré. Elle le met dans un sachet. Le sachet craque un peu. Merci. Merci. Bravo, Victorino. Tu as dit les mots. Victorino tient le sachet. Le pain est encore chaud. Il est chaud, papa. Oui. On le sent. Tu as dit bonjour. Tu as dit s'il te plaît. Tu as dit merci. Bonjour. S'il te plaît. Merci. C'est ça. Bravo. Tu as fait du bon travail. Victorino pose le sachet contre sa veste. La chaleur passe un peu. On reste encore un petit moment ? Oui. Je tiens le pain.</t>
+          <t>La vapeur fait un nuage sur la vitre. Un petit rond s'ouvre, puis se referme. Ça sent le cacao, tout chaud. Une cuillère tinte contre une tasse. Le store rayé claque, dehors. Tu as vu le nuage, Victorino ? Il s'ouvre. Puis il part. C'est la vapeur du cacao. Le trottoir est encore un peu mouillé. Une feuille collée brille près du pas. On essuie tes chaussures. Voilà. J'ai les joues froides. On entre. Tu restes près de moi. En ce moment, Victorino tient la manche. La cloche de la porte fait ding. L'air est chaud, comme un câlin. Le bois du comptoir est lisse. De la mousse blanche dort dans une tasse. Celle-là. Elle a de la mousse. Le cacao bien chaud. La dame essuie encore une tasse. Le torchon est à carreaux rouges. On attend un peu. Elle a les mains prises. Victorino regarde la tasse. Il avance le doigt vers la vitre. Je veux celle-là. Tu demandes, Victorino. La dame se tourne. Un peu de mousse est sur son tablier.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Georges va à la boulangerie. Papa tient sa main. Ça sent le pain chaud. Georges dit : &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. La dame sourit. Georges dit : un pain, s'il te plaît. La dame tend le pain. Georges dit : merci. Papa dit : bonjour. S'il te plaît. Merci. Georges répète. Le pain est chaud. Papa dit merci aussi.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vapeur fait un nuage sur la vitre. Un petit rond s'ouvre, puis se referme. Ça sent le cacao, tout chaud. Une cuillère tinte contre une tasse. Le store rayé claque, dehors. Tu as vu le nuage, Victorino ? Il s'ouvre. Puis il part. C'est la vapeur du cacao. Le trottoir est encore un peu mouillé. Une feuille collée brille près du pas. On essuie tes chaussures. Voilà. J'ai les joues froides. On entre. Tu restes près de moi. En ce moment, Victorino tient la manche. La cloche de la porte fait ding. L'air est chaud, comme un câlin. Le bois du comptoir est lisse. De la mousse blanche dort dans une tasse. Celle-là. Elle a de la mousse. Le cacao bien chaud. La dame essuie encore une tasse. Le torchon est à carreaux rouges. On attend un peu. Elle a les mains prises. Victorino regarde la tasse. Il avance le doigt vers la vitre. Je veux celle-là. Tu demandes, Victorino. La dame se tourne. Un peu de mousse est sur son tablier.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,66 +1329,45 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La vitre de la boulangerie est floue.
-narrateur|Derrière, les pains sont dorés.
-narrateur|Une odeur de beurre passe dehors.
-narrateur|Le trottoir est encore mouillé.
-narrateur|Une petite flaque brille.
-papa|Tu as vu la flaque, Victorino ?
-enfant-m|Oui, papa.
-narrateur|En ce moment, Victorino tient la main de papa.
-narrateur|Ils avancent vers la porte.
-narrateur|La cloche fait ding.
-papa|On est arrivés.
-narrateur|L'air est chaud, dedans.
-narrateur|De la farine blanche dort sur le bois.
-narrateur|Une baguette se tient debout.
-narrateur|Victorino monte un peu sur la pointe.
-enfant-m|Ça sent bon.
-papa|Oui.
-papa|Le pain est chaud.
-papa|Tu as vu la baguette ?
-enfant-m|Elle est grande.
-narrateur|La dame est derrière le comptoir.
-papa|On dit bonjour ?
-enfant-m|Bonjour.
-papa|Bonjour.
-narrateur|La dame écoute.
-papa|Tu veux un pain ?
-enfant-m|Oui.
-papa|On dit s'il te plaît.
-enfant-m|Un pain, s'il te plaît.
-narrateur|La dame prend un pain doré.
-narrateur|Elle le met dans un sachet.
-narrateur|Le sachet craque un peu.
-enfant-m|Merci.
-papa|Merci.
-papa|Bravo, Victorino.
-papa|Tu as dit les mots.
-narrateur|Victorino tient le sachet.
-narrateur|Le pain est encore chaud.
-enfant-m|Il est chaud, papa.
-papa|Oui.
-papa|On le sent.
-papa|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-papa|Tu as dit merci.
-enfant-m|Bonjour.
-enfant-m|S'il te plaît.
-enfant-m|Merci.
-papa|C'est ça.
-papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Victorino pose le sachet contre sa veste.
-narrateur|La chaleur passe un peu.
-papa|On reste encore un petit moment ?
-enfant-m|Oui.
-enfant-m|Je tiens le pain.</t>
+          <t>narrateur|La vapeur fait un nuage sur la vitre.
+narrateur|Un petit rond s'ouvre, puis se referme.
+narrateur|Ça sent le cacao, tout chaud.
+narrateur|Une cuillère tinte contre une tasse.
+narrateur|Le store rayé claque, dehors.
+papa|Tu as vu le nuage, Victorino ?
+enfant-m|Il s'ouvre.
+enfant-m|Puis il part.
+papa|C'est la vapeur du cacao.
+narrateur|Le trottoir est encore un peu mouillé.
+narrateur|Une feuille collée brille près du pas.
+papa|On essuie tes chaussures.
+papa|Voilà.
+enfant-m|J'ai les joues froides.
+papa|On entre.
+papa|Tu restes près de moi.
+narrateur|En ce moment, Victorino tient la manche.
+narrateur|La cloche de la porte fait ding.
+narrateur|L'air est chaud, comme un câlin.
+narrateur|Le bois du comptoir est lisse.
+narrateur|De la mousse blanche dort dans une tasse.
+enfant-m|Celle-là.
+enfant-m|Elle a de la mousse.
+papa|Le cacao bien chaud.
+narrateur|La dame essuie encore une tasse.
+narrateur|Le torchon est à carreaux rouges.
+papa|On attend un peu.
+papa|Elle a les mains prises.
+narrateur|Victorino regarde la tasse.
+narrateur|Il avance le doigt vers la vitre.
+enfant-m|Je veux celle-là.
+papa|Tu demandes, Victorino.
+narrateur|La dame se tourne.
+narrateur|Un peu de mousse est sur son tablier.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>cloche,pain,porte</t>
+          <t>cloche,tasse</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1394,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Victorino parle à la dame. Quels mots dit-il ?</t>
+          <t>Victorino veut le cacao. Que dit-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Georges parle à la dame. Quels mots dit-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino veut le cacao. Que dit-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1425,12 +1409,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>bonjour</t>
+          <t>s'il te plaît</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>bonjour | s'il te plaît | merci | bonjour merci</t>
+          <t>s'il te plaît | merci | bonjour | s'il te plait</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1445,7 +1429,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On salue. On demande. On remercie. Quels mots ?</t>
+          <t>Il dit s'il te plaît. Que dit Victorino ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1566,11 +1550,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Victorino parle à la dame.
-narrateur|Quels mots dit-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorino veut le cacao.
+narrateur|Que dit-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1595,12 +1578,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a dit bonjour. Il a dit s'il te plaît. Il a dit merci. Tu as dit les trois mots. Bravo. Bonjour. S'il te plaît. Merci. Oui. C'est ça. Le sachet reste chaud. Victorino le serre. Tu as fini de tenir le pain ? Oui, papa.</t>
+          <t>Bonjour. Bonjour. Un cacao, s'il te plaît. Avec la mousse. La dame pose la tasse. La mousse tremble un peu. Ça sent le chocolat, tout près. Merci. Merci. Tu as demandé, Victorino. Bravo. Victorino tient l'anse des deux mains. La chaleur passe dans ses doigts. Elle est chaude, papa. On souffle un peu. Il souffle. La mousse fait un petit trou. Un point sur mon nez. Oui. Un point de mousse. La cuillère tinte encore. Le store claque, dehors. On dit au revoir, maintenant. Au revoir. Au revoir. La cloche fait ding, encore. L'air froid revient sur les joues.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Georges a dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. Il a dit s'il te plaît. Il a dit merci. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Bonjour. Bonjour. Un cacao, s'il te plaît. Avec la mousse. La dame pose la tasse. La mousse tremble un peu. Ça sent le chocolat, tout près. Merci. Merci. Tu as demandé, Victorino. Bravo. Victorino tient l'anse des deux mains. La chaleur passe dans ses doigts. Elle est chaude, papa. On souffle un peu. Il souffle. La mousse fait un petit trou. Un point sur mon nez. Oui. Un point de mousse. La cuillère tinte encore. Le store claque, dehors. On dit au revoir, maintenant. Au revoir. Au revoir. La cloche fait ding, encore. L'air froid revient sur les joues.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1739,23 +1722,40 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Victorino a dit bonjour.
-narrateur|Il a dit s'il te plaît.
-narrateur|Il a dit merci.
-papa|Tu as dit les trois mots.
+          <t>enfant-m|Bonjour.
+papa|Bonjour.
+enfant-m|Un cacao, s'il te plaît.
+enfant-m|Avec la mousse.
+narrateur|La dame pose la tasse.
+narrateur|La mousse tremble un peu.
+narrateur|Ça sent le chocolat, tout près.
+enfant-m|Merci.
+papa|Merci.
+papa|Tu as demandé, Victorino.
 papa|Bravo.
-enfant-m|Bonjour.
-enfant-m|S'il te plaît.
-enfant-m|Merci.
+narrateur|Victorino tient l'anse des deux mains.
+narrateur|La chaleur passe dans ses doigts.
+enfant-m|Elle est chaude, papa.
+papa|On souffle un peu.
+narrateur|Il souffle.
+narrateur|La mousse fait un petit trou.
+enfant-m|Un point sur mon nez.
 papa|Oui.
-papa|C'est ça.
-narrateur|Le sachet reste chaud.
-narrateur|Victorino le serre.
-papa|Tu as fini de tenir le pain ?
-enfant-m|Oui, papa.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+papa|Un point de mousse.
+narrateur|La cuillère tinte encore.
+narrateur|Le store claque, dehors.
+papa|On dit au revoir, maintenant.
+enfant-m|Au revoir.
+papa|Au revoir.
+narrateur|La cloche fait ding, encore.
+narrateur|L'air froid revient sur les joues.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>tasse,cuillere</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa ouvre la porte. La cloche fait ding, encore. L'air dehors est plus frais. Le pain est à moi. On le porte ensemble. Victorino tient le sachet. Papa tient sa main. Merci, Victorino. Merci, papa. On rentre ? Oui.</t>
+          <t>Sur le chemin, le foulard sent le cacao. Tu as encore le point ? Un peu. Il est sucré. On le laisse. La feuille n'est plus sur le pas. Le store rayé claque loin derrière. À la maison, ça sent déjà la soupe. Vous sentez le chocolat ? C'est mon foulard. J'ai bu le cacao. Tu as demandé, Victorino ? Bonjour. S'il te plaît. Merci. La mousse a fait un point. Sur le nez ? Oui, maman. Il n'est plus là. Il est dans le foulard. Le nuage de la vitre est parti. Victorino pose le foulard sur la chaise. Ça sent encore le cacao, tout bas.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Georges tient le pain. Papa ouvre la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur le chemin, le foulard sent le cacao. Tu as encore le point ? Un peu. Il est sucré. On le laisse. La feuille n'est plus sur le pas. Le store rayé claque loin derrière. À la maison, ça sent déjà la soupe. Vous sentez le chocolat ? C'est mon foulard. J'ai bu le cacao. Tu as demandé, Victorino ? Bonjour. S'il te plaît. Merci. La mousse a fait un point. Sur le nez ? Oui, maman. Il n'est plus là. Il est dans le foulard. Le nuage de la vitre est parti. Victorino pose le foulard sur la chaise. Ça sent encore le cacao, tout bas.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1916,22 +1916,34 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa ouvre la porte.
-narrateur|La cloche fait ding, encore.
-narrateur|L'air dehors est plus frais.
-enfant-m|Le pain est à moi.
-papa|On le porte ensemble.
-narrateur|Victorino tient le sachet.
-narrateur|Papa tient sa main.
-papa|Merci, Victorino.
-enfant-m|Merci, papa.
-papa|On rentre ?
-enfant-m|Oui.</t>
+          <t>narrateur|Sur le chemin, le foulard sent le cacao.
+papa|Tu as encore le point ?
+enfant-m|Un peu.
+enfant-m|Il est sucré.
+papa|On le laisse.
+narrateur|La feuille n'est plus sur le pas.
+narrateur|Le store rayé claque loin derrière.
+narrateur|À la maison, ça sent déjà la soupe.
+maman|Vous sentez le chocolat ?
+enfant-m|C'est mon foulard.
+enfant-m|J'ai bu le cacao.
+maman|Tu as demandé, Victorino ?
+enfant-m|Bonjour.
+enfant-m|S'il te plaît.
+enfant-m|Merci.
+papa|La mousse a fait un point.
+maman|Sur le nez ?
+enfant-m|Oui, maman.
+maman|Il n'est plus là.
+enfant-m|Il est dans le foulard.
+papa|Le nuage de la vitre est parti.
+narrateur|Victorino pose le foulard sur la chaise.
+narrateur|Ça sent encore le cacao, tout bas.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>porte,cloche</t>
+          <t>pas,porte</t>
         </is>
       </c>
     </row>
@@ -1958,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit bonjour. S'il te plaît. Merci. Bravo. Tu as fait du bon travail. Le pain est à la maison. L'histoire est finie.</t>
+          <t>Le foulard repose sur la chaise. Il sent encore le cacao. Bonne soirée, Victorino. La tasse était chaude. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le foulard repose sur la chaise. Il sent encore le cacao. Bonne soirée, Victorino. La tasse était chaude. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,16 +2110,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai dit bonjour.
-enfant-m|S'il te plaît.
-enfant-m|Merci.
-papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le pain est à la maison.
+          <t>narrateur|Le foulard repose sur la chaise.
+narrateur|Il sent encore le cacao.
+maman|Bonne soirée, Victorino.
+papa|La tasse était chaude.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2126,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2199,6 +2208,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.POL.001-13.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-13.xlsx
@@ -1970,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le foulard repose sur la chaise. Il sent encore le cacao. Bonne soirée, Victorino. La tasse était chaude. L'histoire est finie.</t>
+          <t>Le foulard repose sur la chaise. Il sent encore le cacao. Bonne soirée, Victorino. La tasse était chaude.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le foulard repose sur la chaise. Il sent encore le cacao. Bonne soirée, Victorino. La tasse était chaude. L'histoire est finie.</t>
+          <t>Le foulard repose sur la chaise. Il sent encore le cacao. Bonne soirée, Victorino. La tasse était chaude.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2113,8 +2113,7 @@
           <t>narrateur|Le foulard repose sur la chaise.
 narrateur|Il sent encore le cacao.
 maman|Bonne soirée, Victorino.
-papa|La tasse était chaude.
-narrateur|L'histoire est finie.</t>
+papa|La tasse était chaude.</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2213,6 +2212,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-COL.POL.001-13.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-13.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boulangerie</t>
+          <t>café du village, puis maison</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Georges, papa</t>
+          <t>Victorino, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.POL.001-13.xlsx
+++ b/stories/arbres/ATOM-COL.POL.001-13.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le cacao de Victorino</t>
+          <t>Le pain chaud de Victorino</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>café du village, puis maison</t>
+          <t>trottoir, vitre floue, pains dorés, odeur de beurre, boulangerie</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Victorino veut la tasse de cacao derrière la vitre. Il dit bonjour, s'il te plaît, merci. La mousse laisse un point sur son nez.</t>
+          <t>Une goutte glisse sur la vitre floue. Sur le pain, un éclat de dorure brille. Victorino veut le pain chaud maintenant. Il avance trop vite, sans le mot : la dame ne tourne pas. Il refuse de foncer, dit bonjour. Merci vécu. Le sachet glisse. Sur le pain, l'éclat de dorure tient.</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vapeur fait un nuage sur la vitre. Un petit rond s'ouvre, puis se referme. Ça sent le cacao, tout chaud. Une cuillère tinte contre une tasse. Le store rayé claque, dehors. Tu as vu le nuage, Victorino ? Il s'ouvre. Puis il part. C'est la vapeur du cacao. Le trottoir est encore un peu mouillé. Une feuille collée brille près du pas. On essuie tes chaussures. Voilà. J'ai les joues froides. On entre. Tu restes près de moi. En ce moment, Victorino tient la manche. La cloche de la porte fait ding. L'air est chaud, comme un câlin. Le bois du comptoir est lisse. De la mousse blanche dort dans une tasse. Celle-là. Elle a de la mousse. Le cacao bien chaud. La dame essuie encore une tasse. Le torchon est à carreaux rouges. On attend un peu. Elle a les mains prises. Victorino regarde la tasse. Il avance le doigt vers la vitre. Je veux celle-là. Tu demandes, Victorino. La dame se tourne. Un peu de mousse est sur son tablier.</t>
+          <t>Une goutte glisse sur la vitre floue. Derrière, les pains dorés attendent. Ils brillent, papa. Tu les vois, à travers le verre ? Une odeur de beurre court sur le trottoir. Ça sent le beurre, maman. Oui, le long du verre. Le trottoir est mouillé, un peu froid. Mes chaussures font toc. On les entend, sous tes pieds ? Oui, papa. On reste près de la vitre ? Oui, maman. Un pain rond se tient derrière le verre. Sa peau est dorée, un peu lisse. Celui-là, maman. Sur le pain, un éclat de dorure brille. Il est jaune, papa. C'est le pain, sous la lumière. Tu le touches, Victorino ? Victorino pose un doigt sur le verre. Le verre est tiède, un peu flou. Il pique un peu. On pousse la porte ? Oui, maintenant ! En ce moment, Victorino pose la main sur la porte. La cloche fait ding, un peu fort. L'air chaud touche les joues. Ça sent le pain et le beurre. Il est chaud ici. On reste près du bois ? Oui. Une baguette se tient debout, près du bois. Elle est grande, papa. Tu la vois, à côté du pain ? Oui. La dame essuie le bois du comptoir. Le torchon reste dans ses mains. Celui-là, maintenant ! Victorino avance trop vite vers le bois. Sa voix se mélange à la cloche. Oh. La dame ne tourne pas la tête. Le pain rond reste près du bois. Le sourire de Victorino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Elle ne m'entend pas, papa. Tu la vois, Victorino ? Papa se baisse à sa hauteur. L'éclat de dorure tremble, puis tient. Les épaules de Victorino tombent un peu. La baguette attend, là. Le mien sera chaud.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La vapeur fait un nuage sur la vitre. Un petit rond s'ouvre, puis se referme. Ça sent le cacao, tout chaud. Une cuillère tinte contre une tasse. Le store rayé claque, dehors. Tu as vu le nuage, Victorino ? Il s'ouvre. Puis il part. C'est la vapeur du cacao. Le trottoir est encore un peu mouillé. Une feuille collée brille près du pas. On essuie tes chaussures. Voilà. J'ai les joues froides. On entre. Tu restes près de moi. En ce moment, Victorino tient la manche. La cloche de la porte fait ding. L'air est chaud, comme un câlin. Le bois du comptoir est lisse. De la mousse blanche dort dans une tasse. Celle-là. Elle a de la mousse. Le cacao bien chaud. La dame essuie encore une tasse. Le torchon est à carreaux rouges. On attend un peu. Elle a les mains prises. Victorino regarde la tasse. Il avance le doigt vers la vitre. Je veux celle-là. Tu demandes, Victorino. La dame se tourne. Un peu de mousse est sur son tablier.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Une goutte glisse sur la vitre floue. Derrière, les pains dorés attendent. Ils brillent, papa. Tu les vois, à travers le verre ? Une odeur de beurre court sur le trottoir. Ça sent le beurre, maman. Oui, le long du verre. Le trottoir est mouillé, un peu froid. Mes chaussures font toc. On les entend, sous tes pieds ? Oui, papa. On reste près de la vitre ? Oui, maman. Un pain rond se tient derrière le verre. Sa peau est dorée, un peu lisse. Celui-là, maman. Sur le pain, un &lt;emphasis level="moderate"&gt;éclat de dorure&lt;/emphasis&gt; brille. Il est jaune, papa. C'est le pain, sous la lumière. Tu le touches, Victorino ? Victorino pose un doigt sur le verre. Le verre est tiède, un peu flou. Il pique un peu. On pousse la porte ? Oui, maintenant ! En ce moment, Victorino pose la main sur la porte. La cloche fait ding, un peu fort. L'air chaud touche les joues. Ça sent le pain et le beurre. Il est chaud ici. On reste près du bois ? Oui. Une baguette se tient debout, près du bois. Elle est grande, papa. Tu la vois, à côté du pain ? Oui. La dame essuie le bois du comptoir. Le torchon reste dans ses mains. Celui-là, maintenant ! Victorino avance trop vite vers le bois. Sa voix se mélange à la cloche. Oh. La dame ne tourne pas la tête. Le pain rond reste près du bois. Le sourire de Victorino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Elle ne m'entend pas, papa. Tu la vois, Victorino ? Papa se baisse à sa hauteur. L'éclat de dorure tremble, puis tient. Les épaules de Victorino tombent un peu. La baguette attend, là. Le mien sera chaud.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Georges va à la boulangerie. Papa tient sa main. Ça sent le pain chaud. Georges dit : &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. La dame sourit. Georges dit : un pain, s'il te plaît. La dame tend le pain. Georges dit : merci. Papa dit : bonjour. S'il te plaît. Merci. Georges répète. Le pain est chaud. Papa dit merci aussi.&lt;/slow&gt; [pause]</t>
+          <t>Une goutte glisse sur la vitre floue. Derrière, les pains dorés attendent. Ils brillent, papa. Tu les vois, à travers le verre ? Une odeur de beurre court sur le trottoir. Ça sent le beurre, maman. Oui, le long du verre. Le trottoir est mouillé, un peu froid. Mes chaussures font toc. On les entend, sous tes pieds ? Oui, papa. On reste près de la vitre ? Oui, maman. Un pain rond se tient derrière le verre. Sa peau est dorée, un peu lisse. Celui-là, maman. Sur le pain, un &lt;emphasis&gt;éclat de dorure&lt;/emphasis&gt; brille. Il est jaune, papa. C'est le pain, sous la lumière. Tu le touches, Victorino ? Victorino pose un doigt sur le verre. Le verre est tiède, un peu flou. Il pique un peu. On pousse la porte ? Oui, maintenant ! En ce moment, Victorino pose la main sur la porte. La cloche fait ding, un peu fort. L'air chaud touche les joues. Ça sent le pain et le beurre. Il est chaud ici. On reste près du bois ? Oui. Une baguette se tient debout, près du bois. Elle est grande, papa. Tu la vois, à côté du pain ? Oui. La dame essuie le bois du comptoir. Le torchon reste dans ses mains. Celui-là, maintenant ! Victorino avance trop vite vers le bois. Sa voix se mélange à la cloche. Oh. La dame ne tourne pas la tête. Le pain rond reste près du bois. Le sourire de Victorino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Elle ne m'entend pas, papa. Tu la vois, Victorino ? Papa se baisse à sa hauteur. L'éclat de dorure tremble, puis tient. Les épaules de Victorino tombent un peu. La baguette attend, là. Le mien sera chaud. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1246,18 +1246,18 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1280,30 +1280,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>bonjour</t>
+          <t>éclat de dorure</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1324,50 +1324,73 @@
         <v>50</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=il_veut_le_pain_chaud_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La vapeur fait un nuage sur la vitre.
-narrateur|Un petit rond s'ouvre, puis se referme.
-narrateur|Ça sent le cacao, tout chaud.
-narrateur|Une cuillère tinte contre une tasse.
-narrateur|Le store rayé claque, dehors.
-papa|Tu as vu le nuage, Victorino ?
-enfant-m|Il s'ouvre.
-enfant-m|Puis il part.
-papa|C'est la vapeur du cacao.
-narrateur|Le trottoir est encore un peu mouillé.
-narrateur|Une feuille collée brille près du pas.
-papa|On essuie tes chaussures.
-papa|Voilà.
-enfant-m|J'ai les joues froides.
-papa|On entre.
-papa|Tu restes près de moi.
-narrateur|En ce moment, Victorino tient la manche.
-narrateur|La cloche de la porte fait ding.
-narrateur|L'air est chaud, comme un câlin.
-narrateur|Le bois du comptoir est lisse.
-narrateur|De la mousse blanche dort dans une tasse.
-enfant-m|Celle-là.
-enfant-m|Elle a de la mousse.
-papa|Le cacao bien chaud.
-narrateur|La dame essuie encore une tasse.
-narrateur|Le torchon est à carreaux rouges.
-papa|On attend un peu.
-papa|Elle a les mains prises.
-narrateur|Victorino regarde la tasse.
-narrateur|Il avance le doigt vers la vitre.
-enfant-m|Je veux celle-là.
-papa|Tu demandes, Victorino.
-narrateur|La dame se tourne.
-narrateur|Un peu de mousse est sur son tablier.</t>
+          <t>narrateur|Une goutte glisse sur la vitre floue.
+narrateur|Derrière, les pains dorés attendent.
+enfant-m|Ils brillent, papa.
+papa|Tu les vois, à travers le verre ?
+narrateur|Une odeur de beurre court sur le trottoir.
+enfant-m|Ça sent le beurre, maman.
+maman|Oui, le long du verre.
+narrateur|Le trottoir est mouillé, un peu froid.
+enfant-m|Mes chaussures font toc.
+papa|On les entend, sous tes pieds ?
+enfant-m|Oui, papa.
+maman|On reste près de la vitre ?
+enfant-m|Oui, maman.
+narrateur|Un pain rond se tient derrière le verre.
+narrateur|Sa peau est dorée, un peu lisse.
+enfant-m|Celui-là, maman.
+narrateur|Sur le pain, un éclat de dorure brille.
+enfant-m|Il est jaune, papa.
+papa|C'est le pain, sous la lumière.
+maman|Tu le touches, Victorino ?
+narrateur|Victorino pose un doigt sur le verre.
+narrateur|Le verre est tiède, un peu flou.
+enfant-m|Il pique un peu.
+papa|On pousse la porte ?
+enfant-m|Oui, maintenant !
+narrateur|En ce moment, Victorino pose la main sur la porte.
+narrateur|La cloche fait ding, un peu fort.
+narrateur|L'air chaud touche les joues.
+narrateur|Ça sent le pain et le beurre.
+enfant-m|Il est chaud ici.
+maman|On reste près du bois ?
+enfant-m|Oui.
+narrateur|Une baguette se tient debout, près du bois.
+enfant-m|Elle est grande, papa.
+papa|Tu la vois, à côté du pain ?
+enfant-m|Oui.
+narrateur|La dame essuie le bois du comptoir.
+narrateur|Le torchon reste dans ses mains.
+enfant-m|Celui-là, maintenant !
+narrateur|Victorino avance trop vite vers le bois.
+narrateur|Sa voix se mélange à la cloche.
+enfant-m|Oh.
+narrateur|La dame ne tourne pas la tête.
+narrateur|Le pain rond reste près du bois.
+narrateur|Le sourire de Victorino disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+enfant-m|Elle ne m'entend pas, papa.
+papa|Tu la vois, Victorino ?
+narrateur|Papa se baisse à sa hauteur.
+narrateur|L'éclat de dorure tremble, puis tient.
+narrateur|Les épaules de Victorino tombent un peu.
+maman|La baguette attend, là.
+enfant-m|Le mien sera chaud.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>cloche,tasse</t>
+          <t>cloche,porte,pas</t>
         </is>
       </c>
     </row>
@@ -1394,27 +1417,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Victorino veut le cacao. Que dit-il ?</t>
+          <t>Victorino parle à la dame. Quels mots dit-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Victorino veut le cacao. Que dit-il ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Victorino parle à la &lt;emphasis level="moderate"&gt;dame&lt;/emphasis&gt;. Quels mots dit-il ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Georges parle à la dame. Quels mots dit-il ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Victorino parle à la &lt;emphasis&gt;dame&lt;/emphasis&gt;. Quels mots dit-il ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>s'il te plaît</t>
+          <t>bonjour</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>s'il te plaît | merci | bonjour | s'il te plait</t>
+          <t>bonjour | s'il te plaît | merci | bonjour merci</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1429,7 +1452,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il dit s'il te plaît. Que dit Victorino ?</t>
+          <t>Il dit bonjour. Quels mots dit Victorino ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1467,7 +1490,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1475,10 +1498,10 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1493,34 +1516,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>dame</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1529,13 +1556,13 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
@@ -1545,13 +1572,13 @@
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=il_dit_bonjour; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Victorino veut le cacao.
-narrateur|Que dit-il ?</t>
+          <t>narrateur|Victorino parle à la dame.
+narrateur|Quels mots dit-il ?</t>
         </is>
       </c>
     </row>
@@ -1578,17 +1605,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Bonjour. Bonjour. Un cacao, s'il te plaît. Avec la mousse. La dame pose la tasse. La mousse tremble un peu. Ça sent le chocolat, tout près. Merci. Merci. Tu as demandé, Victorino. Bravo. Victorino tient l'anse des deux mains. La chaleur passe dans ses doigts. Elle est chaude, papa. On souffle un peu. Il souffle. La mousse fait un petit trou. Un point sur mon nez. Oui. Un point de mousse. La cuillère tinte encore. Le store claque, dehors. On dit au revoir, maintenant. Au revoir. Au revoir. La cloche fait ding, encore. L'air froid revient sur les joues.</t>
+          <t>Victorino avance trop vite vers le bois. Le pain, maintenant ! Sa voix se mélange à la cloche. Oh. Le torchon ne bouge pas. Le sourire ne revient pas. Victorino refuse de foncer. Il recule d'un pas, près du bois. Tu veux venir près du bois ? Papa reste à sa hauteur. Victorino écoute la cloche, un instant. Par la vitre, l'éclat de dorure brille. Bonjour. Bonjour. Un pain, s'il te plaît. Celui de la vitre. Derrière le bois, une main se tend. Le papier enveloppe le pain rond. Le sachet est chaud contre la veste. Merci. Merci, Victorino. Papa a entendu toute la phrase. Le ventre de Victorino se desserre. Il est chaud, maman. Tu as les mains dessus ? Oui, maman. Le papier est un peu gras, un peu tiède. Ça sent le beurre. On sort ? Oui, maman. Victorino tient le sachet à deux mains. Le fond du sac est tiède.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Bonjour. Bonjour. Un cacao, s'il te plaît. Avec la mousse. La dame pose la tasse. La mousse tremble un peu. Ça sent le chocolat, tout près. Merci. Merci. Tu as demandé, Victorino. Bravo. Victorino tient l'anse des deux mains. La chaleur passe dans ses doigts. Elle est chaude, papa. On souffle un peu. Il souffle. La mousse fait un petit trou. Un point sur mon nez. Oui. Un point de mousse. La cuillère tinte encore. Le store claque, dehors. On dit au revoir, maintenant. Au revoir. Au revoir. La cloche fait ding, encore. L'air froid revient sur les joues.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Victorino avance trop vite vers le bois. Le pain, maintenant ! Sa voix se mélange à la cloche. Oh. Le torchon ne bouge pas. Le sourire ne revient pas. Victorino refuse de foncer. Il recule d'un pas, près du bois. Tu veux venir près du bois ? Papa reste à sa hauteur. Victorino écoute la cloche, un instant. Par la vitre, l'éclat de dorure brille. &lt;emphasis level="moderate"&gt;Bonjour&lt;/emphasis&gt;. Bonjour. Un pain, s'il te plaît. Celui de la vitre. Derrière le bois, une main se tend. Le papier enveloppe le pain rond. Le sachet est chaud contre la veste. Merci. Merci, Victorino. Papa a entendu toute la phrase. Le ventre de Victorino se desserre. Il est chaud, maman. Tu as les mains dessus ? Oui, maman. Le papier est un peu gras, un peu tiède. Ça sent le beurre. On sort ? Oui, maman. Victorino tient le sachet à deux mains. Le fond du sac est tiède.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Georges a dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. Il a dit s'il te plaît. Il a dit merci. Papa était là.&lt;/slow&gt; [pause]</t>
+          <t>Victorino avance trop vite vers le bois. Le pain, maintenant ! Sa voix se mélange à la cloche. Oh. Le torchon ne bouge pas. Le sourire ne revient pas. Victorino refuse de foncer. Il recule d'un pas, près du bois. Tu veux venir près du bois ? Papa reste à sa hauteur. Victorino écoute la cloche, un instant. Par la vitre, l'éclat de dorure brille. &lt;emphasis&gt;Bonjour&lt;/emphasis&gt;. Bonjour. Un pain, s'il te plaît. Celui de la vitre. Derrière le bois, une main se tend. Le papier enveloppe le pain rond. Le sachet est chaud contre la veste. Merci. Merci, Victorino. Papa a entendu toute la phrase. Le ventre de Victorino se desserre. Il est chaud, maman. Tu as les mains dessus ? Oui, maman. Le papier est un peu gras, un peu tiède. Ça sent le beurre. On sort ? Oui, maman. Victorino tient le sachet à deux mains. Le fond du sac est tiède. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1635,18 +1662,18 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1669,30 +1696,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>bonjour</t>
+          <t>Bonjour</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>380</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1701,10 +1728,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1713,47 +1740,52 @@
         <v>50</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=il_salue_puis_demande; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>enfant-m|Bonjour.
-papa|Bonjour.
-enfant-m|Un cacao, s'il te plaît.
-enfant-m|Avec la mousse.
-narrateur|La dame pose la tasse.
-narrateur|La mousse tremble un peu.
-narrateur|Ça sent le chocolat, tout près.
+          <t>narrateur|Victorino avance trop vite vers le bois.
+enfant-m|Le pain, maintenant !
+narrateur|Sa voix se mélange à la cloche.
+enfant-m|Oh.
+narrateur|Le torchon ne bouge pas.
+narrateur|Le sourire ne revient pas.
+narrateur|Victorino refuse de foncer.
+narrateur|Il recule d'un pas, près du bois.
+papa|Tu veux venir près du bois ?
+narrateur|Papa reste à sa hauteur.
+narrateur|Victorino écoute la cloche, un instant.
+narrateur|Par la vitre, l'éclat de dorure brille.
+enfant-m|Bonjour.
+maman|Bonjour.
+enfant-m|Un pain, s'il te plaît.
+enfant-m|Celui de la vitre.
+narrateur|Derrière le bois, une main se tend.
+narrateur|Le papier enveloppe le pain rond.
+narrateur|Le sachet est chaud contre la veste.
 enfant-m|Merci.
-papa|Merci.
-papa|Tu as demandé, Victorino.
-papa|Bravo.
-narrateur|Victorino tient l'anse des deux mains.
-narrateur|La chaleur passe dans ses doigts.
-enfant-m|Elle est chaude, papa.
-papa|On souffle un peu.
-narrateur|Il souffle.
-narrateur|La mousse fait un petit trou.
-enfant-m|Un point sur mon nez.
-papa|Oui.
-papa|Un point de mousse.
-narrateur|La cuillère tinte encore.
-narrateur|Le store claque, dehors.
-papa|On dit au revoir, maintenant.
-enfant-m|Au revoir.
-papa|Au revoir.
-narrateur|La cloche fait ding, encore.
-narrateur|L'air froid revient sur les joues.</t>
+papa|Merci, Victorino.
+narrateur|Papa a entendu toute la phrase.
+narrateur|Le ventre de Victorino se desserre.
+enfant-m|Il est chaud, maman.
+maman|Tu as les mains dessus ?
+enfant-m|Oui, maman.
+narrateur|Le papier est un peu gras, un peu tiède.
+enfant-m|Ça sent le beurre.
+maman|On sort ?
+enfant-m|Oui, maman.
+narrateur|Victorino tient le sachet à deux mains.
+narrateur|Le fond du sac est tiède.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>tasse,cuillere</t>
+          <t>papier,cloche</t>
         </is>
       </c>
     </row>
@@ -1780,17 +1812,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sur le chemin, le foulard sent le cacao. Tu as encore le point ? Un peu. Il est sucré. On le laisse. La feuille n'est plus sur le pas. Le store rayé claque loin derrière. À la maison, ça sent déjà la soupe. Vous sentez le chocolat ? C'est mon foulard. J'ai bu le cacao. Tu as demandé, Victorino ? Bonjour. S'il te plaît. Merci. La mousse a fait un point. Sur le nez ? Oui, maman. Il n'est plus là. Il est dans le foulard. Le nuage de la vitre est parti. Victorino pose le foulard sur la chaise. Ça sent encore le cacao, tout bas.</t>
+          <t>Ils passent le pas de bois. La cloche fait ding. L'air du trottoir revient sur les joues. Victorino tire le sachet trop vite. Je le montre, d'un coup ! Le papier glisse entre les doigts. Le pain rond penche vers le sol. Oh. Victorino avance les mains. Puis il s'arrête net. Attends, je regarde. Papa attend, sans parler. Victorino refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Il ramène le sachet contre sa veste. Il écoute le trottoir, un instant. Il est chaud, papa. Tu le portes jusqu'à la rue ? Oui, papa. On marche ? Oui, maman. Une goutte glisse du verre, dehors. Elle fait un trait sur la vitre floue. Comme au début. Tu la vois, sur le verre ? Oui, maman. Victorino serre le sachet contre lui. Il reste chaud. On rentre. Le trottoir est froid, un peu lisse. Je l'entends, papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Sur le chemin, le foulard sent le cacao. Tu as encore le point ? Un peu. Il est sucré. On le laisse. La feuille n'est plus sur le pas. Le store rayé claque loin derrière. À la maison, ça sent déjà la soupe. Vous sentez le chocolat ? C'est mon foulard. J'ai bu le cacao. Tu as demandé, Victorino ? Bonjour. S'il te plaît. Merci. La mousse a fait un point. Sur le nez ? Oui, maman. Il n'est plus là. Il est dans le foulard. Le nuage de la vitre est parti. Victorino pose le foulard sur la chaise. Ça sent encore le cacao, tout bas.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ils passent le pas de bois. La cloche fait ding. L'air du trottoir revient sur les joues. Victorino tire le &lt;emphasis level="moderate"&gt;sachet&lt;/emphasis&gt; trop vite. Je le montre, d'un coup ! Le papier glisse entre les doigts. Le pain rond penche vers le sol. Oh. Victorino avance les mains. Puis il s'arrête net. Attends, je regarde. Papa attend, sans parler. Victorino refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Il ramène le sachet contre sa veste. Il écoute le trottoir, un instant. Il est chaud, papa. Tu le portes jusqu'à la rue ? Oui, papa. On marche ? Oui, maman. Une goutte glisse du verre, dehors. Elle fait un trait sur la vitre floue. Comme au début. Tu la vois, sur le verre ? Oui, maman. Victorino serre le sachet contre lui. Il reste chaud. On rentre. Le trottoir est froid, un peu lisse. Je l'entends, papa.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Georges tient le pain. Papa ouvre la porte.&lt;/slow&gt; [pause]</t>
+          <t>Ils passent le pas de bois. La cloche fait ding. L'air du trottoir revient sur les joues. Victorino tire le &lt;emphasis&gt;sachet&lt;/emphasis&gt; trop vite. Je le montre, d'un coup ! Le papier glisse entre les doigts. Le pain rond penche vers le sol. Oh. Victorino avance les mains. Puis il s'arrête net. Attends, je regarde. Papa attend, sans parler. Victorino refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Il ramène le sachet contre sa veste. Il écoute le trottoir, un instant. Il est chaud, papa. Tu le portes jusqu'à la rue ? Oui, papa. On marche ? Oui, maman. Une goutte glisse du verre, dehors. Elle fait un trait sur la vitre floue. Comme au début. Tu la vois, sur le verre ? Oui, maman. Victorino serre le sachet contre lui. Il reste chaud. On rentre. Le trottoir est froid, un peu lisse. Je l'entends, papa. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1837,18 +1869,18 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1869,28 +1901,32 @@
       <c r="AG5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>sachet</t>
+        </is>
+      </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>380</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1899,10 +1935,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1911,39 +1947,51 @@
         <v>50</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_foncer_quand_le_sachet_glisse; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sur le chemin, le foulard sent le cacao.
-papa|Tu as encore le point ?
-enfant-m|Un peu.
-enfant-m|Il est sucré.
-papa|On le laisse.
-narrateur|La feuille n'est plus sur le pas.
-narrateur|Le store rayé claque loin derrière.
-narrateur|À la maison, ça sent déjà la soupe.
-maman|Vous sentez le chocolat ?
-enfant-m|C'est mon foulard.
-enfant-m|J'ai bu le cacao.
-maman|Tu as demandé, Victorino ?
-enfant-m|Bonjour.
-enfant-m|S'il te plaît.
-enfant-m|Merci.
-papa|La mousse a fait un point.
-maman|Sur le nez ?
+          <t>narrateur|Ils passent le pas de bois.
+narrateur|La cloche fait ding.
+narrateur|L'air du trottoir revient sur les joues.
+narrateur|Victorino tire le sachet trop vite.
+enfant-m|Je le montre, d'un coup !
+narrateur|Le papier glisse entre les doigts.
+narrateur|Le pain rond penche vers le sol.
+enfant-m|Oh.
+narrateur|Victorino avance les mains.
+narrateur|Puis il s'arrête net.
+enfant-m|Attends, je regarde.
+narrateur|Papa attend, sans parler.
+narrateur|Victorino refuse de foncer, cette fois.
+narrateur|Ses mains se ferment, puis s'ouvrent.
+narrateur|Il ramène le sachet contre sa veste.
+narrateur|Il écoute le trottoir, un instant.
+enfant-m|Il est chaud, papa.
+papa|Tu le portes jusqu'à la rue ?
+enfant-m|Oui, papa.
+maman|On marche ?
 enfant-m|Oui, maman.
-maman|Il n'est plus là.
-enfant-m|Il est dans le foulard.
-papa|Le nuage de la vitre est parti.
-narrateur|Victorino pose le foulard sur la chaise.
-narrateur|Ça sent encore le cacao, tout bas.</t>
+narrateur|Une goutte glisse du verre, dehors.
+narrateur|Elle fait un trait sur la vitre floue.
+enfant-m|Comme au début.
+maman|Tu la vois, sur le verre ?
+enfant-m|Oui, maman.
+narrateur|Victorino serre le sachet contre lui.
+enfant-m|Il reste chaud.
+papa|On rentre.
+narrateur|Le trottoir est froid, un peu lisse.
+enfant-m|Je l'entends, papa.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>pas,porte</t>
+          <t>pas,papier</t>
         </is>
       </c>
     </row>
@@ -1970,17 +2018,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le foulard repose sur la chaise. Il sent encore le cacao. Bonne soirée, Victorino. La tasse était chaude.</t>
+          <t>Ils s'arrêtent sous la vitre floue. La goutte a fini sa course. Le pain brillait, papa. Tu le vois, comme dans la boutique ? Oui, sur le pain. Victorino pose le sachet contre la veste. On le garde au chaud ? Oui, maman. Ça sent le beurre, maman. Il est contre toi. Une vapeur monte du papier. Victorino respire, plus large. On rentre ? Oui. Les joues de Victorino se réchauffent. Le sachet reste tiède sous la main. On le voit, maman. Tu le vois sur le pain ? Oui, l'éclat. L'éclat de dorure tient sur le pain.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le foulard repose sur la chaise. Il sent encore le cacao. Bonne soirée, Victorino. La tasse était chaude.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils s'arrêtent sous la vitre floue. La goutte a fini sa course. Le pain brillait, papa. Tu le vois, comme dans la boutique ? Oui, sur le pain. Victorino pose le sachet contre la veste. On le garde au chaud ? Oui, maman. Ça sent le beurre, maman. Il est contre toi. Une vapeur monte du papier. Victorino respire, plus large. On rentre ? Oui. Les joues de Victorino se réchauffent. Le sachet reste tiède sous la main. On le voit, maman. Tu le vois sur le pain ? Oui, l'éclat. L'&lt;emphasis level="moderate"&gt;éclat de dorure&lt;/emphasis&gt; tient sur le pain.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils s'arrêtent sous la vitre floue. La goutte a fini sa course. Le pain brillait, papa. Tu le vois, comme dans la boutique ? Oui, sur le pain. Victorino pose le sachet contre la veste. On le garde au chaud ? Oui, maman. Ça sent le beurre, maman. Il est contre toi. Une vapeur monte du papier. Victorino respire, plus large. On rentre ? Oui. Les joues de Victorino se réchauffent. Le sachet reste tiède sous la main. On le voit, maman. Tu le vois sur le pain ? Oui, l'éclat. L'&lt;emphasis&gt;éclat de dorure&lt;/emphasis&gt; tient sur le pain.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2027,7 +2075,7 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
@@ -2035,10 +2083,10 @@
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2047,12 +2095,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2061,17 +2109,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de dorure</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2080,11 +2132,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2093,27 +2145,52 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_le_pain; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Le foulard repose sur la chaise.
-narrateur|Il sent encore le cacao.
-maman|Bonne soirée, Victorino.
-papa|La tasse était chaude.</t>
+          <t>narrateur|Ils s'arrêtent sous la vitre floue.
+narrateur|La goutte a fini sa course.
+enfant-m|Le pain brillait, papa.
+papa|Tu le vois, comme dans la boutique ?
+enfant-m|Oui, sur le pain.
+narrateur|Victorino pose le sachet contre la veste.
+maman|On le garde au chaud ?
+enfant-m|Oui, maman.
+enfant-m|Ça sent le beurre, maman.
+maman|Il est contre toi.
+narrateur|Une vapeur monte du papier.
+narrateur|Victorino respire, plus large.
+papa|On rentre ?
+enfant-m|Oui.
+narrateur|Les joues de Victorino se réchauffent.
+narrateur|Le sachet reste tiède sous la main.
+enfant-m|On le voit, maman.
+maman|Tu le vois sur le pain ?
+enfant-m|Oui, l'éclat.
+narrateur|L'éclat de dorure tient sur le pain.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>pain,verre</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2219,6 +2296,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
